--- a/extenbooks/XS006_extenbook.xlsx
+++ b/extenbooks/XS006_extenbook.xlsx
@@ -653,7 +653,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -708,10 +708,10 @@
         <v>1926</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0660499297091747</v>
+        <v>0.06604992970917478</v>
       </c>
       <c r="C5" t="n">
-        <v>99.21785819593644</v>
+        <v>99.21785819593643</v>
       </c>
       <c r="D5" t="n">
         <v>79.727</v>
@@ -722,10 +722,10 @@
         <v>1927</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0658245241092112</v>
+        <v>0.06582452410921125</v>
       </c>
       <c r="C6" t="n">
-        <v>99.01962729698552</v>
+        <v>99.01962729698553</v>
       </c>
       <c r="D6" t="n">
         <v>80.892</v>
@@ -764,7 +764,7 @@
         <v>1930</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0697082875045793</v>
+        <v>0.06970828750457933</v>
       </c>
       <c r="C9" t="n">
         <v>91.01494858854144</v>
@@ -778,7 +778,7 @@
         <v>1931</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0712158701676197</v>
+        <v>0.07121587016761978</v>
       </c>
       <c r="C10" t="n">
         <v>80.26985367641122</v>
@@ -792,7 +792,7 @@
         <v>1932</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0690615755705552</v>
+        <v>0.06906157557055527</v>
       </c>
       <c r="C11" t="n">
         <v>73.39643055484115</v>
@@ -820,7 +820,7 @@
         <v>1934</v>
       </c>
       <c r="B13" t="n">
-        <v>0.069225173996983</v>
+        <v>0.06922517399698302</v>
       </c>
       <c r="C13" t="n">
         <v>72.13128734578216</v>
@@ -848,7 +848,7 @@
         <v>1936</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0683345791434312</v>
+        <v>0.06833457914343127</v>
       </c>
       <c r="C15" t="n">
         <v>76.12454536477391</v>
@@ -862,7 +862,7 @@
         <v>1937</v>
       </c>
       <c r="B16" t="n">
-        <v>0.07280341772487289</v>
+        <v>0.07280341772487296</v>
       </c>
       <c r="C16" t="n">
         <v>77.66735773712426</v>
@@ -876,7 +876,7 @@
         <v>1938</v>
       </c>
       <c r="B17" t="n">
-        <v>0.07394165154781911</v>
+        <v>0.07394165154781916</v>
       </c>
       <c r="C17" t="n">
         <v>75.33761201026756</v>
@@ -890,7 +890,7 @@
         <v>1939</v>
       </c>
       <c r="B18" t="n">
-        <v>0.07329074778531609</v>
+        <v>0.07329074778531619</v>
       </c>
       <c r="C18" t="n">
         <v>74.59294505202064</v>
@@ -904,7 +904,7 @@
         <v>1940</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0730173241438403</v>
+        <v>0.07301732414384035</v>
       </c>
       <c r="C19" t="n">
         <v>78.21624970067333</v>
@@ -918,7 +918,7 @@
         <v>1941</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0734034900154369</v>
+        <v>0.07340349001543692</v>
       </c>
       <c r="C20" t="n">
         <v>86.70911593161935</v>
@@ -946,7 +946,7 @@
         <v>1943</v>
       </c>
       <c r="B22" t="n">
-        <v>0.07510356327630641</v>
+        <v>0.07510356327630643</v>
       </c>
       <c r="C22" t="n">
         <v>89.63018737561302</v>
@@ -960,7 +960,7 @@
         <v>1944</v>
       </c>
       <c r="B23" t="n">
-        <v>0.07627250746847949</v>
+        <v>0.07627250746847952</v>
       </c>
       <c r="C23" t="n">
         <v>89.33938835148243</v>
@@ -974,7 +974,7 @@
         <v>1945</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0728470773951079</v>
+        <v>0.07284707739510794</v>
       </c>
       <c r="C24" t="n">
         <v>97.11788183800748</v>
@@ -1002,7 +1002,7 @@
         <v>1947</v>
       </c>
       <c r="B26" t="n">
-        <v>0.07350898639159439</v>
+        <v>0.07350898639159446</v>
       </c>
       <c r="C26" t="n">
         <v>140.6964787377904</v>
@@ -1016,7 +1016,7 @@
         <v>1948</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0764211297497452</v>
+        <v>0.07642112974974527</v>
       </c>
       <c r="C27" t="n">
         <v>154.875664629068</v>
@@ -1030,7 +1030,7 @@
         <v>1949</v>
       </c>
       <c r="B28" t="n">
-        <v>0.07631570296704231</v>
+        <v>0.07631570296704236</v>
       </c>
       <c r="C28" t="n">
         <v>158.6575587619228</v>
@@ -1044,7 +1044,7 @@
         <v>1950</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0743916673821689</v>
+        <v>0.07439166738216897</v>
       </c>
       <c r="C29" t="n">
         <v>178.2798738926147</v>
@@ -1058,7 +1058,7 @@
         <v>1951</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0780505614275272</v>
+        <v>0.07805056142752728</v>
       </c>
       <c r="C30" t="n">
         <v>194.5471330164521</v>
@@ -1072,10 +1072,10 @@
         <v>1952</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0785756567426403</v>
+        <v>0.07857565674264036</v>
       </c>
       <c r="C31" t="n">
-        <v>206.570216455382</v>
+        <v>206.5702164553819</v>
       </c>
       <c r="D31" t="n">
         <v>201.502</v>
@@ -1086,7 +1086,7 @@
         <v>1953</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0796307932824673</v>
+        <v>0.07963079328246733</v>
       </c>
       <c r="C32" t="n">
         <v>217.7210368325078</v>
@@ -1100,7 +1100,7 @@
         <v>1954</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0798769509954762</v>
+        <v>0.07987695099547626</v>
       </c>
       <c r="C33" t="n">
         <v>224.7083169767935</v>
@@ -1114,7 +1114,7 @@
         <v>1955</v>
       </c>
       <c r="B34" t="n">
-        <v>0.07794971454241351</v>
+        <v>0.07794971454241356</v>
       </c>
       <c r="C34" t="n">
         <v>247.649377469867</v>
@@ -1128,7 +1128,7 @@
         <v>1956</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0793908575397862</v>
+        <v>0.07939085753978622</v>
       </c>
       <c r="C35" t="n">
         <v>275.8350358208909</v>
@@ -1142,7 +1142,7 @@
         <v>1957</v>
       </c>
       <c r="B36" t="n">
-        <v>0.08091514683127971</v>
+        <v>0.08091514683127979</v>
       </c>
       <c r="C36" t="n">
         <v>297.131173214452</v>
@@ -1156,7 +1156,7 @@
         <v>1958</v>
       </c>
       <c r="B37" t="n">
-        <v>0.08020206886896369</v>
+        <v>0.08020206886896371</v>
       </c>
       <c r="C37" t="n">
         <v>303.470036040506</v>
@@ -1170,7 +1170,7 @@
         <v>1959</v>
       </c>
       <c r="B38" t="n">
-        <v>0.08098791640724801</v>
+        <v>0.08098791640724808</v>
       </c>
       <c r="C38" t="n">
         <v>317.3541763401915</v>
@@ -1184,7 +1184,7 @@
         <v>1960</v>
       </c>
       <c r="B39" t="n">
-        <v>0.08245078420188109</v>
+        <v>0.08245078420188111</v>
       </c>
       <c r="C39" t="n">
         <v>324.3703965652497</v>
@@ -1198,7 +1198,7 @@
         <v>1961</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0824762848060888</v>
+        <v>0.08247628480608882</v>
       </c>
       <c r="C40" t="n">
         <v>332.7037347786313</v>
@@ -1212,7 +1212,7 @@
         <v>1962</v>
       </c>
       <c r="B41" t="n">
-        <v>0.0827950510989364</v>
+        <v>0.08279505109893649</v>
       </c>
       <c r="C41" t="n">
         <v>344.2482052285193</v>
@@ -1226,7 +1226,7 @@
         <v>1963</v>
       </c>
       <c r="B42" t="n">
-        <v>0.0833999657812084</v>
+        <v>0.08339996578120848</v>
       </c>
       <c r="C42" t="n">
         <v>356.4397906455158</v>
@@ -1240,7 +1240,7 @@
         <v>1964</v>
       </c>
       <c r="B43" t="n">
-        <v>0.0838598964125349</v>
+        <v>0.08385989641253498</v>
       </c>
       <c r="C43" t="n">
         <v>378.2670542979229</v>
@@ -1254,7 +1254,7 @@
         <v>1965</v>
       </c>
       <c r="B44" t="n">
-        <v>0.08413271043844329</v>
+        <v>0.08413271043844338</v>
       </c>
       <c r="C44" t="n">
         <v>407.9245171056672</v>
@@ -1268,7 +1268,7 @@
         <v>1966</v>
       </c>
       <c r="B45" t="n">
-        <v>0.08356952758590171</v>
+        <v>0.08356952758590172</v>
       </c>
       <c r="C45" t="n">
         <v>448.5267356537076</v>
@@ -1282,7 +1282,7 @@
         <v>1967</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0833859941714207</v>
+        <v>0.08338599417142079</v>
       </c>
       <c r="C46" t="n">
         <v>489.7650098693491</v>
@@ -1296,7 +1296,7 @@
         <v>1968</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0831205950548958</v>
+        <v>0.08312059505489586</v>
       </c>
       <c r="C47" t="n">
         <v>542.5755977050926</v>
@@ -1310,7 +1310,7 @@
         <v>1969</v>
       </c>
       <c r="B48" t="n">
-        <v>0.0822386993305927</v>
+        <v>0.08223869933059277</v>
       </c>
       <c r="C48" t="n">
         <v>601.9712383936233</v>
@@ -1324,7 +1324,7 @@
         <v>1970</v>
       </c>
       <c r="B49" t="n">
-        <v>0.08088493329932871</v>
+        <v>0.08088493329932873</v>
       </c>
       <c r="C49" t="n">
         <v>666.3831688538669</v>
@@ -1338,7 +1338,7 @@
         <v>1971</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0803488105571923</v>
+        <v>0.08034881055719233</v>
       </c>
       <c r="C50" t="n">
         <v>734.2712651248133</v>
@@ -1352,7 +1352,7 @@
         <v>1972</v>
       </c>
       <c r="B51" t="n">
-        <v>0.08076126099468341</v>
+        <v>0.08076126099468349</v>
       </c>
       <c r="C51" t="n">
         <v>801.5509317069542</v>
@@ -1380,7 +1380,7 @@
         <v>1974</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0767080041879392</v>
+        <v>0.07670800418793923</v>
       </c>
       <c r="C53" t="n">
         <v>1119.400209138383</v>
@@ -1394,7 +1394,7 @@
         <v>1975</v>
       </c>
       <c r="B54" t="n">
-        <v>0.08020252343871689</v>
+        <v>0.08020252343871692</v>
       </c>
       <c r="C54" t="n">
         <v>1246.335062617772</v>
@@ -1408,7 +1408,7 @@
         <v>1976</v>
       </c>
       <c r="B55" t="n">
-        <v>0.08179460308954579</v>
+        <v>0.08179460308954585</v>
       </c>
       <c r="C55" t="n">
         <v>1371.794579644241</v>
@@ -1422,7 +1422,7 @@
         <v>1977</v>
       </c>
       <c r="B56" t="n">
-        <v>0.08315139604681521</v>
+        <v>0.08315139604681525</v>
       </c>
       <c r="C56" t="n">
         <v>1530.761077665188</v>
@@ -1436,7 +1436,7 @@
         <v>1978</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0842458502629983</v>
+        <v>0.08424585026299838</v>
       </c>
       <c r="C57" t="n">
         <v>1745.534123388127</v>
@@ -1450,7 +1450,7 @@
         <v>1979</v>
       </c>
       <c r="B58" t="n">
-        <v>0.08546240944679249</v>
+        <v>0.08546240944679255</v>
       </c>
       <c r="C58" t="n">
         <v>2016.690999182254</v>
@@ -1464,7 +1464,7 @@
         <v>1980</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0843598497208181</v>
+        <v>0.08435984972081813</v>
       </c>
       <c r="C59" t="n">
         <v>2324.310780838796</v>
@@ -1478,7 +1478,7 @@
         <v>1981</v>
       </c>
       <c r="B60" t="n">
-        <v>0.08718536707058699</v>
+        <v>0.08718536707058709</v>
       </c>
       <c r="C60" t="n">
         <v>2632.664285767203</v>
@@ -1492,7 +1492,7 @@
         <v>1982</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0904768162439336</v>
+        <v>0.09047681624393361</v>
       </c>
       <c r="C61" t="n">
         <v>2796.447680158588</v>
@@ -1506,7 +1506,7 @@
         <v>1983</v>
       </c>
       <c r="B62" t="n">
-        <v>0.08984663856490099</v>
+        <v>0.08984663856490105</v>
       </c>
       <c r="C62" t="n">
         <v>2879.142546279102</v>
@@ -1520,10 +1520,10 @@
         <v>1984</v>
       </c>
       <c r="B63" t="n">
-        <v>0.0907075266139139</v>
+        <v>0.09070752661391397</v>
       </c>
       <c r="C63" t="n">
-        <v>3055.955651006669</v>
+        <v>3055.95565100667</v>
       </c>
       <c r="D63" t="n">
         <v>2993.218</v>
@@ -1548,7 +1548,7 @@
         <v>1986</v>
       </c>
       <c r="B65" t="n">
-        <v>0.09114587768881589</v>
+        <v>0.09114587768881599</v>
       </c>
       <c r="C65" t="n">
         <v>3385.930564230765</v>
@@ -1562,7 +1562,7 @@
         <v>1987</v>
       </c>
       <c r="B66" t="n">
-        <v>0.0908343752520565</v>
+        <v>0.09083437525205657</v>
       </c>
       <c r="C66" t="n">
         <v>3566.320858243699</v>
@@ -1576,7 +1576,7 @@
         <v>1988</v>
       </c>
       <c r="B67" t="n">
-        <v>0.09101628897703019</v>
+        <v>0.09101628897703024</v>
       </c>
       <c r="C67" t="n">
         <v>3797.86408143987</v>
@@ -1590,7 +1590,7 @@
         <v>1989</v>
       </c>
       <c r="B68" t="n">
-        <v>0.0928074408161649</v>
+        <v>0.09280744081616492</v>
       </c>
       <c r="C68" t="n">
         <v>4029.561716365089</v>
@@ -1604,7 +1604,7 @@
         <v>1990</v>
       </c>
       <c r="B69" t="n">
-        <v>0.0905860185847272</v>
+        <v>0.09058601858472726</v>
       </c>
       <c r="C69" t="n">
         <v>4270.719993788062</v>
@@ -1618,7 +1618,7 @@
         <v>1991</v>
       </c>
       <c r="B70" t="n">
-        <v>0.0909459378768319</v>
+        <v>0.09094593787683192</v>
       </c>
       <c r="C70" t="n">
         <v>4381.850134110044</v>
@@ -1632,7 +1632,7 @@
         <v>1992</v>
       </c>
       <c r="B71" t="n">
-        <v>0.09130585716893649</v>
+        <v>0.09130585716893658</v>
       </c>
       <c r="C71" t="n">
         <v>4539.794204017248</v>
@@ -1646,7 +1646,7 @@
         <v>1993</v>
       </c>
       <c r="B72" t="n">
-        <v>0.0916657764610412</v>
+        <v>0.09166577646104124</v>
       </c>
       <c r="C72" t="n">
         <v>4765.485059325251</v>
@@ -1674,7 +1674,7 @@
         <v>1995</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0923856150452505</v>
+        <v>0.09238561504525056</v>
       </c>
       <c r="C74" t="n">
         <v>5356.596266769102</v>
@@ -1688,7 +1688,7 @@
         <v>1996</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0927455343373552</v>
+        <v>0.09274553433735522</v>
       </c>
       <c r="C75" t="n">
         <v>5662.035992293144</v>
@@ -1702,7 +1702,7 @@
         <v>1997</v>
       </c>
       <c r="B76" t="n">
-        <v>0.09310545362945979</v>
+        <v>0.09310545362945988</v>
       </c>
       <c r="C76" t="n">
         <v>6014.653333680543</v>
@@ -1716,7 +1716,7 @@
         <v>1998</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0934653729215645</v>
+        <v>0.09346537292156454</v>
       </c>
       <c r="C77" t="n">
         <v>6396.503812141911</v>
@@ -1744,7 +1744,7 @@
         <v>2000</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0941852115057739</v>
+        <v>0.09418521150577397</v>
       </c>
       <c r="C79" t="n">
         <v>7361.51385651135</v>
@@ -1758,7 +1758,7 @@
         <v>2001</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0945451307978786</v>
+        <v>0.09454513079787863</v>
       </c>
       <c r="C80" t="n">
         <v>7792.808040240707</v>
@@ -1772,7 +1772,7 @@
         <v>2002</v>
       </c>
       <c r="B81" t="n">
-        <v>0.09490505008998321</v>
+        <v>0.09490505008998329</v>
       </c>
       <c r="C81" t="n">
         <v>8082.459930363552</v>
@@ -1786,7 +1786,7 @@
         <v>2003</v>
       </c>
       <c r="B82" t="n">
-        <v>0.09526496938208789</v>
+        <v>0.09526496938208795</v>
       </c>
       <c r="C82" t="n">
         <v>8330.563325919195</v>
@@ -1800,7 +1800,7 @@
         <v>2004</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0956248886741926</v>
+        <v>0.09562488867419261</v>
       </c>
       <c r="C83" t="n">
         <v>8960.736277754495</v>
@@ -1814,7 +1814,7 @@
         <v>2005</v>
       </c>
       <c r="B84" t="n">
-        <v>0.0959848079662972</v>
+        <v>0.09598480796629727</v>
       </c>
       <c r="C84" t="n">
         <v>9710.662435224274</v>
@@ -1828,7 +1828,7 @@
         <v>2006</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0963447272584019</v>
+        <v>0.09634472725840193</v>
       </c>
       <c r="C85" t="n">
         <v>10480.62144776589</v>
@@ -1842,7 +1842,7 @@
         <v>2007</v>
       </c>
       <c r="B86" t="n">
-        <v>0.09670464655050651</v>
+        <v>0.09670464655050659</v>
       </c>
       <c r="C86" t="n">
         <v>11017.50973042573</v>
@@ -1856,7 +1856,7 @@
         <v>2008</v>
       </c>
       <c r="B87" t="n">
-        <v>0.09706456584261119</v>
+        <v>0.09706456584261125</v>
       </c>
       <c r="C87" t="n">
         <v>11696.43267541223</v>
@@ -1870,7 +1870,7 @@
         <v>2009</v>
       </c>
       <c r="B88" t="n">
-        <v>0.0974244851347159</v>
+        <v>0.09742448513471591</v>
       </c>
       <c r="C88" t="n">
         <v>11240.11297133088</v>
@@ -1884,7 +1884,7 @@
         <v>2010</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0977844044268205</v>
+        <v>0.09778440442682057</v>
       </c>
       <c r="C89" t="n">
         <v>11408.40315225199</v>
@@ -1898,7 +1898,7 @@
         <v>2011</v>
       </c>
       <c r="B90" t="n">
-        <v>0.0981443237189252</v>
+        <v>0.09814432371892523</v>
       </c>
       <c r="C90" t="n">
         <v>11799.35185600587</v>
@@ -1946,14 +1946,14 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B96" t="n">
-        <v>98.09999999999999</v>
+        <v>0.06604992970917478</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -1963,20 +1963,20 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="B97" t="n">
-        <v>77.76900000000001</v>
+        <v>0.06582452410921125</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -1986,16 +1986,16 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="B98" t="n">
-        <v>0.0660499297091747</v>
+        <v>0.06644584576356589</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2009,20 +2009,20 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="B99" t="n">
-        <v>99.21785819593644</v>
+        <v>0.0685516207978954</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2032,20 +2032,20 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="B100" t="n">
-        <v>79.727</v>
+        <v>0.06970828750457933</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2055,16 +2055,16 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0658245241092112</v>
+        <v>0.07121587016761978</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1927</v>
+        <v>1932</v>
       </c>
       <c r="B102" t="n">
-        <v>99.01962729698552</v>
+        <v>0.06906157557055527</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2101,20 +2101,20 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
       <c r="B103" t="n">
-        <v>80.892</v>
+        <v>0.0672095231856014</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2124,16 +2124,16 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1928</v>
+        <v>1934</v>
       </c>
       <c r="B104" t="n">
-        <v>0.06644584576356589</v>
+        <v>0.06922517399698302</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2147,20 +2147,20 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1928</v>
+        <v>1935</v>
       </c>
       <c r="B105" t="n">
-        <v>99.61651252904326</v>
+        <v>0.0702047564150169</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1928</v>
+        <v>1936</v>
       </c>
       <c r="B106" t="n">
-        <v>81.55</v>
+        <v>0.06833457914343127</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2193,16 +2193,16 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1929</v>
+        <v>1937</v>
       </c>
       <c r="B107" t="n">
-        <v>0.0685516207978954</v>
+        <v>0.07280341772487296</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2216,20 +2216,20 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1929</v>
+        <v>1938</v>
       </c>
       <c r="B108" t="n">
-        <v>97.14330619893347</v>
+        <v>0.07394165154781916</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2239,20 +2239,20 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="B109" t="n">
-        <v>81.369</v>
+        <v>0.07329074778531619</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2262,16 +2262,16 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="B110" t="n">
-        <v>0.0697082875045793</v>
+        <v>0.07301732414384035</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2285,20 +2285,20 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1930</v>
+        <v>1941</v>
       </c>
       <c r="B111" t="n">
-        <v>91.01494858854144</v>
+        <v>0.07340349001543692</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2308,20 +2308,20 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1930</v>
+        <v>1942</v>
       </c>
       <c r="B112" t="n">
-        <v>76.628</v>
+        <v>0.07494795054322489</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2331,16 +2331,16 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1931</v>
+        <v>1943</v>
       </c>
       <c r="B113" t="n">
-        <v>0.0712158701676197</v>
+        <v>0.07510356327630643</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2354,20 +2354,20 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1931</v>
+        <v>1944</v>
       </c>
       <c r="B114" t="n">
-        <v>80.26985367641122</v>
+        <v>0.07627250746847952</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2377,20 +2377,20 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1931</v>
+        <v>1945</v>
       </c>
       <c r="B115" t="n">
-        <v>68.367</v>
+        <v>0.07284707739510794</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1932</v>
+        <v>1946</v>
       </c>
       <c r="B116" t="n">
-        <v>0.0690615755705552</v>
+        <v>0.0719963271564506</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2423,20 +2423,20 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1932</v>
+        <v>1947</v>
       </c>
       <c r="B117" t="n">
-        <v>73.39643055484115</v>
+        <v>0.07350898639159446</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1932</v>
+        <v>1948</v>
       </c>
       <c r="B118" t="n">
-        <v>61.955</v>
+        <v>0.07642112974974527</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2469,16 +2469,16 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="B119" t="n">
-        <v>0.0672095231856014</v>
+        <v>0.07631570296704236</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2492,20 +2492,20 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1933</v>
+        <v>1950</v>
       </c>
       <c r="B120" t="n">
-        <v>72.71164502154747</v>
+        <v>0.07439166738216897</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2515,20 +2515,20 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1933</v>
+        <v>1951</v>
       </c>
       <c r="B121" t="n">
-        <v>60.951</v>
+        <v>0.07805056142752728</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2538,16 +2538,16 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1934</v>
+        <v>1952</v>
       </c>
       <c r="B122" t="n">
-        <v>0.069225173996983</v>
+        <v>0.07857565674264036</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2561,20 +2561,20 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1934</v>
+        <v>1953</v>
       </c>
       <c r="B123" t="n">
-        <v>72.13128734578216</v>
+        <v>0.07963079328246733</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2584,20 +2584,20 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1934</v>
+        <v>1954</v>
       </c>
       <c r="B124" t="n">
-        <v>61.071</v>
+        <v>0.07987695099547626</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2607,16 +2607,16 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1935</v>
+        <v>1955</v>
       </c>
       <c r="B125" t="n">
-        <v>0.0702047564150169</v>
+        <v>0.07794971454241356</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2630,20 +2630,20 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1935</v>
+        <v>1956</v>
       </c>
       <c r="B126" t="n">
-        <v>70.47787092446919</v>
+        <v>0.07939085753978622</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1935</v>
+        <v>1957</v>
       </c>
       <c r="B127" t="n">
-        <v>61.096</v>
+        <v>0.08091514683127979</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2676,16 +2676,16 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1936</v>
+        <v>1958</v>
       </c>
       <c r="B128" t="n">
-        <v>0.0683345791434312</v>
+        <v>0.08020206886896371</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -2699,20 +2699,20 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1936</v>
+        <v>1959</v>
       </c>
       <c r="B129" t="n">
-        <v>76.12454536477391</v>
+        <v>0.08098791640724808</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -2722,20 +2722,20 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1936</v>
+        <v>1960</v>
       </c>
       <c r="B130" t="n">
-        <v>64.14700000000001</v>
+        <v>0.08245078420188111</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2745,16 +2745,16 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1937</v>
+        <v>1961</v>
       </c>
       <c r="B131" t="n">
-        <v>0.07280341772487289</v>
+        <v>0.08247628480608882</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -2768,20 +2768,20 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1937</v>
+        <v>1962</v>
       </c>
       <c r="B132" t="n">
-        <v>77.66735773712426</v>
+        <v>0.08279505109893649</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -2791,20 +2791,20 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1937</v>
+        <v>1963</v>
       </c>
       <c r="B133" t="n">
-        <v>67.517</v>
+        <v>0.08339996578120848</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2814,16 +2814,16 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1938</v>
+        <v>1964</v>
       </c>
       <c r="B134" t="n">
-        <v>0.07394165154781911</v>
+        <v>0.08385989641253498</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -2837,20 +2837,20 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1938</v>
+        <v>1965</v>
       </c>
       <c r="B135" t="n">
-        <v>75.33761201026756</v>
+        <v>0.08413271043844338</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -2860,20 +2860,20 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1938</v>
+        <v>1966</v>
       </c>
       <c r="B136" t="n">
-        <v>66.28100000000001</v>
+        <v>0.08356952758590172</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2883,16 +2883,16 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1939</v>
+        <v>1967</v>
       </c>
       <c r="B137" t="n">
-        <v>0.07329074778531609</v>
+        <v>0.08338599417142079</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -2906,20 +2906,20 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1939</v>
+        <v>1968</v>
       </c>
       <c r="B138" t="n">
-        <v>74.59294505202064</v>
+        <v>0.08312059505489586</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2929,20 +2929,20 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1939</v>
+        <v>1969</v>
       </c>
       <c r="B139" t="n">
-        <v>66.35599999999999</v>
+        <v>0.08223869933059277</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -2952,16 +2952,16 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1940</v>
+        <v>1970</v>
       </c>
       <c r="B140" t="n">
-        <v>0.0730173241438403</v>
+        <v>0.08088493329932873</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2975,20 +2975,20 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1940</v>
+        <v>1971</v>
       </c>
       <c r="B141" t="n">
-        <v>78.21624970067333</v>
+        <v>0.08034881055719233</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -2998,20 +2998,20 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1940</v>
+        <v>1972</v>
       </c>
       <c r="B142" t="n">
-        <v>69.879</v>
+        <v>0.08076126099468349</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3021,16 +3021,16 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1941</v>
+        <v>1973</v>
       </c>
       <c r="B143" t="n">
-        <v>0.0734034900154369</v>
+        <v>0.07840359212395449</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -3044,20 +3044,20 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1941</v>
+        <v>1974</v>
       </c>
       <c r="B144" t="n">
-        <v>86.70911593161935</v>
+        <v>0.07670800418793923</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3067,20 +3067,20 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1941</v>
+        <v>1975</v>
       </c>
       <c r="B145" t="n">
-        <v>76.541</v>
+        <v>0.08020252343871692</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3090,16 +3090,16 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1942</v>
+        <v>1976</v>
       </c>
       <c r="B146" t="n">
-        <v>0.07494795054322489</v>
+        <v>0.08179460308954585</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -3113,20 +3113,20 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1942</v>
+        <v>1977</v>
       </c>
       <c r="B147" t="n">
-        <v>90.67772495400968</v>
+        <v>0.08315139604681525</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3136,20 +3136,20 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1942</v>
+        <v>1978</v>
       </c>
       <c r="B148" t="n">
-        <v>80.512</v>
+        <v>0.08424585026299838</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3159,16 +3159,16 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1943</v>
+        <v>1979</v>
       </c>
       <c r="B149" t="n">
-        <v>0.07510356327630641</v>
+        <v>0.08546240944679255</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -3182,20 +3182,20 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1943</v>
+        <v>1980</v>
       </c>
       <c r="B150" t="n">
-        <v>89.63018737561302</v>
+        <v>0.08435984972081813</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3205,20 +3205,20 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1943</v>
+        <v>1981</v>
       </c>
       <c r="B151" t="n">
-        <v>81.242</v>
+        <v>0.08718536707058709</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3228,16 +3228,16 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1944</v>
+        <v>1982</v>
       </c>
       <c r="B152" t="n">
-        <v>0.07627250746847949</v>
+        <v>0.09047681624393361</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -3251,20 +3251,20 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1944</v>
+        <v>1983</v>
       </c>
       <c r="B153" t="n">
-        <v>89.33938835148243</v>
+        <v>0.08984663856490105</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3274,20 +3274,20 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1944</v>
+        <v>1984</v>
       </c>
       <c r="B154" t="n">
-        <v>82.345</v>
+        <v>0.09070752661391397</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3297,16 +3297,16 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1945</v>
+        <v>1985</v>
       </c>
       <c r="B155" t="n">
-        <v>0.0728470773951079</v>
+        <v>0.0914270920178915</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3320,20 +3320,20 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1945</v>
+        <v>1986</v>
       </c>
       <c r="B156" t="n">
-        <v>97.11788183800748</v>
+        <v>0.09114587768881599</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3343,20 +3343,20 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1945</v>
+        <v>1987</v>
       </c>
       <c r="B157" t="n">
-        <v>90.328</v>
+        <v>0.09083437525205657</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3366,16 +3366,16 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1946</v>
+        <v>1988</v>
       </c>
       <c r="B158" t="n">
-        <v>0.0719963271564506</v>
+        <v>0.09101628897703024</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -3389,20 +3389,20 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1946</v>
+        <v>1989</v>
       </c>
       <c r="B159" t="n">
-        <v>117.586674473305</v>
+        <v>0.09280744081616492</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3412,20 +3412,20 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1946</v>
+        <v>1990</v>
       </c>
       <c r="B160" t="n">
-        <v>109.554</v>
+        <v>0.09058601858472726</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3435,16 +3435,16 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1947</v>
+        <v>1991</v>
       </c>
       <c r="B161" t="n">
-        <v>0.07350898639159439</v>
+        <v>0.09094593787683192</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3458,20 +3458,20 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1947</v>
+        <v>1992</v>
       </c>
       <c r="B162" t="n">
-        <v>140.6964787377904</v>
+        <v>0.09130585716893658</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3481,20 +3481,20 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1947</v>
+        <v>1993</v>
       </c>
       <c r="B163" t="n">
-        <v>131.622</v>
+        <v>0.09166577646104124</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3504,16 +3504,16 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1948</v>
+        <v>1994</v>
       </c>
       <c r="B164" t="n">
-        <v>0.0764211297497452</v>
+        <v>0.0920256957531459</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -3527,20 +3527,20 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1948</v>
+        <v>1995</v>
       </c>
       <c r="B165" t="n">
-        <v>154.875664629068</v>
+        <v>0.09238561504525056</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3550,20 +3550,20 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1948</v>
+        <v>1996</v>
       </c>
       <c r="B166" t="n">
-        <v>146.79</v>
+        <v>0.09274553433735522</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3573,16 +3573,16 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1949</v>
+        <v>1997</v>
       </c>
       <c r="B167" t="n">
-        <v>0.07631570296704231</v>
+        <v>0.09310545362945988</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -3596,20 +3596,20 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1949</v>
+        <v>1998</v>
       </c>
       <c r="B168" t="n">
-        <v>158.6575587619228</v>
+        <v>0.09346537292156454</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3619,20 +3619,20 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1949</v>
+        <v>1999</v>
       </c>
       <c r="B169" t="n">
-        <v>155.144</v>
+        <v>0.0938252922136692</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3642,16 +3642,16 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="B170" t="n">
-        <v>0.0743916673821689</v>
+        <v>0.09418521150577397</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1950</v>
+        <v>2001</v>
       </c>
       <c r="B171" t="n">
-        <v>178.2798738926147</v>
+        <v>0.09454513079787863</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3688,20 +3688,20 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1950</v>
+        <v>2002</v>
       </c>
       <c r="B172" t="n">
-        <v>171.295</v>
+        <v>0.09490505008998329</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3711,16 +3711,16 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1951</v>
+        <v>2003</v>
       </c>
       <c r="B173" t="n">
-        <v>0.0780505614275272</v>
+        <v>0.09526496938208795</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -3734,20 +3734,20 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1951</v>
+        <v>2004</v>
       </c>
       <c r="B174" t="n">
-        <v>194.5471330164521</v>
+        <v>0.09562488867419261</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3757,20 +3757,20 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1951</v>
+        <v>2005</v>
       </c>
       <c r="B175" t="n">
-        <v>189.284</v>
+        <v>0.09598480796629727</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3780,16 +3780,16 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1952</v>
+        <v>2006</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0785756567426403</v>
+        <v>0.09634472725840193</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -3803,20 +3803,20 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1952</v>
+        <v>2007</v>
       </c>
       <c r="B177" t="n">
-        <v>206.570216455382</v>
+        <v>0.09670464655050659</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -3826,20 +3826,20 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1952</v>
+        <v>2008</v>
       </c>
       <c r="B178" t="n">
-        <v>201.502</v>
+        <v>0.09706456584261125</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -3849,16 +3849,16 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1953</v>
+        <v>2009</v>
       </c>
       <c r="B179" t="n">
-        <v>0.0796307932824673</v>
+        <v>0.09742448513471591</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -3872,20 +3872,20 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1953</v>
+        <v>2010</v>
       </c>
       <c r="B180" t="n">
-        <v>217.7210368325078</v>
+        <v>0.09778440442682057</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -3895,20 +3895,20 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1953</v>
+        <v>2011</v>
       </c>
       <c r="B181" t="n">
-        <v>213.013</v>
+        <v>0.09814432371892523</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-dcorpnew</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -3918,20 +3918,20 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1954</v>
+        <v>1925</v>
       </c>
       <c r="B182" t="n">
-        <v>0.0798769509954762</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -3947,10 +3947,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1954</v>
+        <v>1926</v>
       </c>
       <c r="B183" t="n">
-        <v>224.7083169767935</v>
+        <v>99.21785819593643</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -3970,14 +3970,14 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1954</v>
+        <v>1927</v>
       </c>
       <c r="B184" t="n">
-        <v>222.866</v>
+        <v>99.01962729698553</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -3993,14 +3993,14 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1955</v>
+        <v>1928</v>
       </c>
       <c r="B185" t="n">
-        <v>0.07794971454241351</v>
+        <v>99.61651252904326</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4016,10 +4016,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1955</v>
+        <v>1929</v>
       </c>
       <c r="B186" t="n">
-        <v>247.649377469867</v>
+        <v>97.14330619893347</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -4039,14 +4039,14 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1955</v>
+        <v>1930</v>
       </c>
       <c r="B187" t="n">
-        <v>243.021</v>
+        <v>91.01494858854144</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4062,14 +4062,14 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1956</v>
+        <v>1931</v>
       </c>
       <c r="B188" t="n">
-        <v>0.0793908575397862</v>
+        <v>80.26985367641122</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4085,10 +4085,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1956</v>
+        <v>1932</v>
       </c>
       <c r="B189" t="n">
-        <v>275.8350358208909</v>
+        <v>73.39643055484115</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -4108,14 +4108,14 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1956</v>
+        <v>1933</v>
       </c>
       <c r="B190" t="n">
-        <v>271.506</v>
+        <v>72.71164502154747</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4131,14 +4131,14 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1957</v>
+        <v>1934</v>
       </c>
       <c r="B191" t="n">
-        <v>0.08091514683127971</v>
+        <v>72.13128734578216</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4154,10 +4154,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1957</v>
+        <v>1935</v>
       </c>
       <c r="B192" t="n">
-        <v>297.131173214452</v>
+        <v>70.47787092446919</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -4177,14 +4177,14 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1957</v>
+        <v>1936</v>
       </c>
       <c r="B193" t="n">
-        <v>292.041</v>
+        <v>76.12454536477391</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4200,14 +4200,14 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1958</v>
+        <v>1937</v>
       </c>
       <c r="B194" t="n">
-        <v>0.08020206886896369</v>
+        <v>77.66735773712426</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4223,10 +4223,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1958</v>
+        <v>1938</v>
       </c>
       <c r="B195" t="n">
-        <v>303.470036040506</v>
+        <v>75.33761201026756</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -4246,14 +4246,14 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1958</v>
+        <v>1939</v>
       </c>
       <c r="B196" t="n">
-        <v>301.41</v>
+        <v>74.59294505202064</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4269,14 +4269,14 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1959</v>
+        <v>1940</v>
       </c>
       <c r="B197" t="n">
-        <v>0.08098791640724801</v>
+        <v>78.21624970067333</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4292,10 +4292,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1959</v>
+        <v>1941</v>
       </c>
       <c r="B198" t="n">
-        <v>317.3541763401915</v>
+        <v>86.70911593161935</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -4315,14 +4315,14 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1959</v>
+        <v>1942</v>
       </c>
       <c r="B199" t="n">
-        <v>314.077</v>
+        <v>90.67772495400968</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4338,14 +4338,14 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1960</v>
+        <v>1943</v>
       </c>
       <c r="B200" t="n">
-        <v>0.08245078420188109</v>
+        <v>89.63018737561302</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4361,10 +4361,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1960</v>
+        <v>1944</v>
       </c>
       <c r="B201" t="n">
-        <v>324.3703965652497</v>
+        <v>89.33938835148243</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -4384,14 +4384,14 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1960</v>
+        <v>1945</v>
       </c>
       <c r="B202" t="n">
-        <v>323.054</v>
+        <v>97.11788183800748</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4407,14 +4407,14 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1961</v>
+        <v>1946</v>
       </c>
       <c r="B203" t="n">
-        <v>0.0824762848060888</v>
+        <v>117.586674473305</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4430,10 +4430,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1961</v>
+        <v>1947</v>
       </c>
       <c r="B204" t="n">
-        <v>332.7037347786313</v>
+        <v>140.6964787377904</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -4453,14 +4453,14 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1961</v>
+        <v>1948</v>
       </c>
       <c r="B205" t="n">
-        <v>331.447</v>
+        <v>154.875664629068</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4476,14 +4476,14 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1962</v>
+        <v>1949</v>
       </c>
       <c r="B206" t="n">
-        <v>0.0827950510989364</v>
+        <v>158.6575587619228</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4499,10 +4499,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1962</v>
+        <v>1950</v>
       </c>
       <c r="B207" t="n">
-        <v>344.2482052285193</v>
+        <v>178.2798738926147</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -4522,14 +4522,14 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1962</v>
+        <v>1951</v>
       </c>
       <c r="B208" t="n">
-        <v>343.819</v>
+        <v>194.5471330164521</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -4545,14 +4545,14 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1963</v>
+        <v>1952</v>
       </c>
       <c r="B209" t="n">
-        <v>0.0833999657812084</v>
+        <v>206.5702164553819</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4568,10 +4568,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1963</v>
+        <v>1953</v>
       </c>
       <c r="B210" t="n">
-        <v>356.4397906455158</v>
+        <v>217.7210368325078</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -4591,14 +4591,14 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1963</v>
+        <v>1954</v>
       </c>
       <c r="B211" t="n">
-        <v>357.177</v>
+        <v>224.7083169767935</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -4614,14 +4614,14 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1964</v>
+        <v>1955</v>
       </c>
       <c r="B212" t="n">
-        <v>0.0838598964125349</v>
+        <v>247.649377469867</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -4637,10 +4637,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1964</v>
+        <v>1956</v>
       </c>
       <c r="B213" t="n">
-        <v>378.2670542979229</v>
+        <v>275.8350358208909</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -4660,14 +4660,14 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1964</v>
+        <v>1957</v>
       </c>
       <c r="B214" t="n">
-        <v>377.34</v>
+        <v>297.131173214452</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -4683,14 +4683,14 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1965</v>
+        <v>1958</v>
       </c>
       <c r="B215" t="n">
-        <v>0.08413271043844329</v>
+        <v>303.470036040506</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -4706,10 +4706,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1965</v>
+        <v>1959</v>
       </c>
       <c r="B216" t="n">
-        <v>407.9245171056672</v>
+        <v>317.3541763401915</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -4729,14 +4729,14 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1965</v>
+        <v>1960</v>
       </c>
       <c r="B217" t="n">
-        <v>407.794</v>
+        <v>324.3703965652497</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -4752,14 +4752,14 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="B218" t="n">
-        <v>0.08356952758590171</v>
+        <v>332.7037347786313</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="B219" t="n">
-        <v>448.5267356537076</v>
+        <v>344.2482052285193</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -4798,14 +4798,14 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="B220" t="n">
-        <v>450.093</v>
+        <v>356.4397906455158</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -4821,14 +4821,14 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="B221" t="n">
-        <v>0.0833859941714207</v>
+        <v>378.2670542979229</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -4844,10 +4844,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B222" t="n">
-        <v>489.7650098693491</v>
+        <v>407.9245171056672</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -4867,14 +4867,14 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B223" t="n">
-        <v>489.841</v>
+        <v>448.5267356537076</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -4890,14 +4890,14 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B224" t="n">
-        <v>0.0831205950548958</v>
+        <v>489.7650098693491</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -4936,14 +4936,14 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B226" t="n">
-        <v>543.968</v>
+        <v>601.9712383936233</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -4959,14 +4959,14 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B227" t="n">
-        <v>0.0822386993305927</v>
+        <v>666.3831688538669</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -4982,10 +4982,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="B228" t="n">
-        <v>601.9712383936233</v>
+        <v>734.2712651248133</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -5005,14 +5005,14 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B229" t="n">
-        <v>602.442</v>
+        <v>801.5509317069542</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5028,14 +5028,14 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="B230" t="n">
-        <v>0.08088493329932871</v>
+        <v>911.0781044266446</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5051,10 +5051,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="B231" t="n">
-        <v>666.3831688538669</v>
+        <v>1119.400209138383</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -5074,14 +5074,14 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="B232" t="n">
-        <v>665.399</v>
+        <v>1246.335062617772</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5097,14 +5097,14 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1971</v>
+        <v>1976</v>
       </c>
       <c r="B233" t="n">
-        <v>0.0803488105571923</v>
+        <v>1371.794579644241</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5120,10 +5120,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1971</v>
+        <v>1977</v>
       </c>
       <c r="B234" t="n">
-        <v>734.2712651248133</v>
+        <v>1530.761077665188</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -5143,14 +5143,14 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1971</v>
+        <v>1978</v>
       </c>
       <c r="B235" t="n">
-        <v>731.546</v>
+        <v>1745.534123388127</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5166,14 +5166,14 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1972</v>
+        <v>1979</v>
       </c>
       <c r="B236" t="n">
-        <v>0.08076126099468341</v>
+        <v>2016.690999182254</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5189,10 +5189,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="B237" t="n">
-        <v>801.5509317069542</v>
+        <v>2324.310780838796</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -5212,14 +5212,14 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1972</v>
+        <v>1981</v>
       </c>
       <c r="B238" t="n">
-        <v>812.716</v>
+        <v>2632.664285767203</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5235,14 +5235,14 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1973</v>
+        <v>1982</v>
       </c>
       <c r="B239" t="n">
-        <v>0.07840359212395449</v>
+        <v>2796.447680158588</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5258,10 +5258,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="B240" t="n">
-        <v>911.0781044266446</v>
+        <v>2879.142546279102</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -5281,14 +5281,14 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1973</v>
+        <v>1984</v>
       </c>
       <c r="B241" t="n">
-        <v>922.601</v>
+        <v>3055.95565100667</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5304,14 +5304,14 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1974</v>
+        <v>1985</v>
       </c>
       <c r="B242" t="n">
-        <v>0.0767080041879392</v>
+        <v>3234.392576412193</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5327,10 +5327,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1974</v>
+        <v>1986</v>
       </c>
       <c r="B243" t="n">
-        <v>1119.400209138383</v>
+        <v>3385.930564230765</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -5350,14 +5350,14 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1974</v>
+        <v>1987</v>
       </c>
       <c r="B244" t="n">
-        <v>1107.313</v>
+        <v>3566.320858243699</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5373,14 +5373,14 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1975</v>
+        <v>1988</v>
       </c>
       <c r="B245" t="n">
-        <v>0.08020252343871689</v>
+        <v>3797.86408143987</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5396,10 +5396,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1975</v>
+        <v>1989</v>
       </c>
       <c r="B246" t="n">
-        <v>1246.335062617772</v>
+        <v>4029.561716365089</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -5419,14 +5419,14 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1975</v>
+        <v>1990</v>
       </c>
       <c r="B247" t="n">
-        <v>1252.398</v>
+        <v>4270.719993788062</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5442,14 +5442,14 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1976</v>
+        <v>1991</v>
       </c>
       <c r="B248" t="n">
-        <v>0.08179460308954579</v>
+        <v>4381.850134110044</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5465,10 +5465,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1976</v>
+        <v>1992</v>
       </c>
       <c r="B249" t="n">
-        <v>1371.794579644241</v>
+        <v>4539.794204017248</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -5488,14 +5488,14 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1976</v>
+        <v>1993</v>
       </c>
       <c r="B250" t="n">
-        <v>1369.168</v>
+        <v>4765.485059325251</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -5511,14 +5511,14 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1977</v>
+        <v>1994</v>
       </c>
       <c r="B251" t="n">
-        <v>0.08315139604681521</v>
+        <v>5044.050858387098</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1977</v>
+        <v>1995</v>
       </c>
       <c r="B252" t="n">
-        <v>1530.761077665188</v>
+        <v>5356.596266769102</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -5557,14 +5557,14 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1977</v>
+        <v>1996</v>
       </c>
       <c r="B253" t="n">
-        <v>1520.544</v>
+        <v>5662.035992293144</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -5580,14 +5580,14 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1978</v>
+        <v>1997</v>
       </c>
       <c r="B254" t="n">
-        <v>0.0842458502629983</v>
+        <v>6014.653333680543</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -5603,10 +5603,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1978</v>
+        <v>1998</v>
       </c>
       <c r="B255" t="n">
-        <v>1745.534123388127</v>
+        <v>6396.503812141911</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -5626,14 +5626,14 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1978</v>
+        <v>1999</v>
       </c>
       <c r="B256" t="n">
-        <v>1723.549</v>
+        <v>6824.093381728645</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -5649,14 +5649,14 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1979</v>
+        <v>2000</v>
       </c>
       <c r="B257" t="n">
-        <v>0.08546240944679249</v>
+        <v>7361.51385651135</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -5672,10 +5672,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1979</v>
+        <v>2001</v>
       </c>
       <c r="B258" t="n">
-        <v>2016.690999182254</v>
+        <v>7792.808040240707</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -5695,14 +5695,14 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1979</v>
+        <v>2002</v>
       </c>
       <c r="B259" t="n">
-        <v>1976.173</v>
+        <v>8082.459930363552</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -5718,14 +5718,14 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="B260" t="n">
-        <v>0.0843598497208181</v>
+        <v>8330.563325919195</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -5741,10 +5741,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1980</v>
+        <v>2004</v>
       </c>
       <c r="B261" t="n">
-        <v>2324.310780838796</v>
+        <v>8960.736277754495</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -5764,14 +5764,14 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1980</v>
+        <v>2005</v>
       </c>
       <c r="B262" t="n">
-        <v>2277.833</v>
+        <v>9710.662435224274</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -5787,14 +5787,14 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1981</v>
+        <v>2006</v>
       </c>
       <c r="B263" t="n">
-        <v>0.08718536707058699</v>
+        <v>10480.62144776589</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -5810,10 +5810,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1981</v>
+        <v>2007</v>
       </c>
       <c r="B264" t="n">
-        <v>2632.664285767203</v>
+        <v>11017.50973042573</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -5833,14 +5833,14 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1981</v>
+        <v>2008</v>
       </c>
       <c r="B265" t="n">
-        <v>2579.67</v>
+        <v>11696.43267541223</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -5856,14 +5856,14 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1982</v>
+        <v>2009</v>
       </c>
       <c r="B266" t="n">
-        <v>0.0904768162439336</v>
+        <v>11240.11297133088</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -5879,10 +5879,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1982</v>
+        <v>2010</v>
       </c>
       <c r="B267" t="n">
-        <v>2796.447680158588</v>
+        <v>11408.40315225199</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -5902,14 +5902,14 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1982</v>
+        <v>2011</v>
       </c>
       <c r="B268" t="n">
-        <v>2756.942</v>
+        <v>11799.35185600587</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>XS006-depr_plus_init</t>
+          <t>XS006-depr_only</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -5925,14 +5925,14 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1983</v>
+        <v>1925</v>
       </c>
       <c r="B269" t="n">
-        <v>0.08984663856490099</v>
+        <v>77.76900000000001</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -5948,14 +5948,14 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1983</v>
+        <v>1926</v>
       </c>
       <c r="B270" t="n">
-        <v>2879.142546279102</v>
+        <v>79.727</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -5971,10 +5971,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1983</v>
+        <v>1927</v>
       </c>
       <c r="B271" t="n">
-        <v>2844.878</v>
+        <v>80.892</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -5994,14 +5994,14 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1984</v>
+        <v>1928</v>
       </c>
       <c r="B272" t="n">
-        <v>0.0907075266139139</v>
+        <v>81.55</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -6017,14 +6017,14 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1984</v>
+        <v>1929</v>
       </c>
       <c r="B273" t="n">
-        <v>3055.955651006669</v>
+        <v>81.369</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6040,10 +6040,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1984</v>
+        <v>1930</v>
       </c>
       <c r="B274" t="n">
-        <v>2993.218</v>
+        <v>76.628</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -6063,14 +6063,14 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1985</v>
+        <v>1931</v>
       </c>
       <c r="B275" t="n">
-        <v>0.0914270920178915</v>
+        <v>68.367</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6086,14 +6086,14 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1985</v>
+        <v>1932</v>
       </c>
       <c r="B276" t="n">
-        <v>3234.392576412193</v>
+        <v>61.955</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6109,10 +6109,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1985</v>
+        <v>1933</v>
       </c>
       <c r="B277" t="n">
-        <v>3158.155</v>
+        <v>60.951</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -6132,14 +6132,14 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1986</v>
+        <v>1934</v>
       </c>
       <c r="B278" t="n">
-        <v>0.09114587768881589</v>
+        <v>61.071</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6155,14 +6155,14 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1986</v>
+        <v>1935</v>
       </c>
       <c r="B279" t="n">
-        <v>3385.930564230765</v>
+        <v>61.096</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6178,10 +6178,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1986</v>
+        <v>1936</v>
       </c>
       <c r="B280" t="n">
-        <v>3317.184</v>
+        <v>64.14700000000001</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -6201,14 +6201,14 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1987</v>
+        <v>1937</v>
       </c>
       <c r="B281" t="n">
-        <v>0.0908343752520565</v>
+        <v>67.517</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6224,14 +6224,14 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1987</v>
+        <v>1938</v>
       </c>
       <c r="B282" t="n">
-        <v>3566.320858243699</v>
+        <v>66.28100000000001</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1987</v>
+        <v>1939</v>
       </c>
       <c r="B283" t="n">
-        <v>3459.685</v>
+        <v>66.35599999999999</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -6270,14 +6270,14 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1988</v>
+        <v>1940</v>
       </c>
       <c r="B284" t="n">
-        <v>0.09101628897703019</v>
+        <v>69.879</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6293,14 +6293,14 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1988</v>
+        <v>1941</v>
       </c>
       <c r="B285" t="n">
-        <v>3797.86408143987</v>
+        <v>76.541</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6316,10 +6316,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1988</v>
+        <v>1942</v>
       </c>
       <c r="B286" t="n">
-        <v>3681.151</v>
+        <v>80.512</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -6339,14 +6339,14 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1989</v>
+        <v>1943</v>
       </c>
       <c r="B287" t="n">
-        <v>0.0928074408161649</v>
+        <v>81.242</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6362,14 +6362,14 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1989</v>
+        <v>1944</v>
       </c>
       <c r="B288" t="n">
-        <v>4029.561716365089</v>
+        <v>82.345</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6385,10 +6385,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1989</v>
+        <v>1945</v>
       </c>
       <c r="B289" t="n">
-        <v>3886.439</v>
+        <v>90.328</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -6408,14 +6408,14 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1990</v>
+        <v>1946</v>
       </c>
       <c r="B290" t="n">
-        <v>0.0905860185847272</v>
+        <v>109.554</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6431,14 +6431,14 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1990</v>
+        <v>1947</v>
       </c>
       <c r="B291" t="n">
-        <v>4270.719993788062</v>
+        <v>131.622</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6454,14 +6454,14 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>1991</v>
+        <v>1948</v>
       </c>
       <c r="B292" t="n">
-        <v>0.0909459378768319</v>
+        <v>146.79</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6477,14 +6477,14 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1991</v>
+        <v>1949</v>
       </c>
       <c r="B293" t="n">
-        <v>4381.850134110044</v>
+        <v>155.144</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6500,14 +6500,14 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>1992</v>
+        <v>1950</v>
       </c>
       <c r="B294" t="n">
-        <v>0.09130585716893649</v>
+        <v>171.295</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6523,14 +6523,14 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>1992</v>
+        <v>1951</v>
       </c>
       <c r="B295" t="n">
-        <v>4539.794204017248</v>
+        <v>189.284</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6546,14 +6546,14 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1993</v>
+        <v>1952</v>
       </c>
       <c r="B296" t="n">
-        <v>0.0916657764610412</v>
+        <v>201.502</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6569,14 +6569,14 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1993</v>
+        <v>1953</v>
       </c>
       <c r="B297" t="n">
-        <v>4765.485059325251</v>
+        <v>213.013</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6592,14 +6592,14 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>1994</v>
+        <v>1954</v>
       </c>
       <c r="B298" t="n">
-        <v>0.0920256957531459</v>
+        <v>222.866</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6615,14 +6615,14 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1994</v>
+        <v>1955</v>
       </c>
       <c r="B299" t="n">
-        <v>5044.050858387098</v>
+        <v>243.021</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -6638,14 +6638,14 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1995</v>
+        <v>1956</v>
       </c>
       <c r="B300" t="n">
-        <v>0.0923856150452505</v>
+        <v>271.506</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -6661,14 +6661,14 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>1995</v>
+        <v>1957</v>
       </c>
       <c r="B301" t="n">
-        <v>5356.596266769102</v>
+        <v>292.041</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -6684,14 +6684,14 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1996</v>
+        <v>1958</v>
       </c>
       <c r="B302" t="n">
-        <v>0.0927455343373552</v>
+        <v>301.41</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -6707,14 +6707,14 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>1996</v>
+        <v>1959</v>
       </c>
       <c r="B303" t="n">
-        <v>5662.035992293144</v>
+        <v>314.077</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -6730,14 +6730,14 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1997</v>
+        <v>1960</v>
       </c>
       <c r="B304" t="n">
-        <v>0.09310545362945979</v>
+        <v>323.054</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -6753,14 +6753,14 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>1997</v>
+        <v>1961</v>
       </c>
       <c r="B305" t="n">
-        <v>6014.653333680543</v>
+        <v>331.447</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -6776,14 +6776,14 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>1998</v>
+        <v>1962</v>
       </c>
       <c r="B306" t="n">
-        <v>0.0934653729215645</v>
+        <v>343.819</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -6799,14 +6799,14 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>1998</v>
+        <v>1963</v>
       </c>
       <c r="B307" t="n">
-        <v>6396.503812141911</v>
+        <v>357.177</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -6822,14 +6822,14 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>1999</v>
+        <v>1964</v>
       </c>
       <c r="B308" t="n">
-        <v>0.0938252922136692</v>
+        <v>377.34</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -6845,14 +6845,14 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1999</v>
+        <v>1965</v>
       </c>
       <c r="B309" t="n">
-        <v>6824.093381728645</v>
+        <v>407.794</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -6868,14 +6868,14 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>2000</v>
+        <v>1966</v>
       </c>
       <c r="B310" t="n">
-        <v>0.0941852115057739</v>
+        <v>450.093</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -6891,14 +6891,14 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>2000</v>
+        <v>1967</v>
       </c>
       <c r="B311" t="n">
-        <v>7361.51385651135</v>
+        <v>489.841</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -6914,14 +6914,14 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>2001</v>
+        <v>1968</v>
       </c>
       <c r="B312" t="n">
-        <v>0.0945451307978786</v>
+        <v>543.968</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6937,14 +6937,14 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2001</v>
+        <v>1969</v>
       </c>
       <c r="B313" t="n">
-        <v>7792.808040240707</v>
+        <v>602.442</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -6960,14 +6960,14 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2002</v>
+        <v>1970</v>
       </c>
       <c r="B314" t="n">
-        <v>0.09490505008998321</v>
+        <v>665.399</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -6983,14 +6983,14 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>2002</v>
+        <v>1971</v>
       </c>
       <c r="B315" t="n">
-        <v>8082.459930363552</v>
+        <v>731.546</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7006,14 +7006,14 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2003</v>
+        <v>1972</v>
       </c>
       <c r="B316" t="n">
-        <v>0.09526496938208789</v>
+        <v>812.716</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7029,14 +7029,14 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>2003</v>
+        <v>1973</v>
       </c>
       <c r="B317" t="n">
-        <v>8330.563325919195</v>
+        <v>922.601</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7052,14 +7052,14 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>2004</v>
+        <v>1974</v>
       </c>
       <c r="B318" t="n">
-        <v>0.0956248886741926</v>
+        <v>1107.313</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7075,14 +7075,14 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>2004</v>
+        <v>1975</v>
       </c>
       <c r="B319" t="n">
-        <v>8960.736277754495</v>
+        <v>1252.398</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7098,14 +7098,14 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>2005</v>
+        <v>1976</v>
       </c>
       <c r="B320" t="n">
-        <v>0.0959848079662972</v>
+        <v>1369.168</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7121,14 +7121,14 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2005</v>
+        <v>1977</v>
       </c>
       <c r="B321" t="n">
-        <v>9710.662435224274</v>
+        <v>1520.544</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7144,14 +7144,14 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2006</v>
+        <v>1978</v>
       </c>
       <c r="B322" t="n">
-        <v>0.0963447272584019</v>
+        <v>1723.549</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7167,14 +7167,14 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2006</v>
+        <v>1979</v>
       </c>
       <c r="B323" t="n">
-        <v>10480.62144776589</v>
+        <v>1976.173</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -7190,14 +7190,14 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>2007</v>
+        <v>1980</v>
       </c>
       <c r="B324" t="n">
-        <v>0.09670464655050651</v>
+        <v>2277.833</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7213,14 +7213,14 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>2007</v>
+        <v>1981</v>
       </c>
       <c r="B325" t="n">
-        <v>11017.50973042573</v>
+        <v>2579.67</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -7236,14 +7236,14 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>2008</v>
+        <v>1982</v>
       </c>
       <c r="B326" t="n">
-        <v>0.09706456584261119</v>
+        <v>2756.942</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -7259,14 +7259,14 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>2008</v>
+        <v>1983</v>
       </c>
       <c r="B327" t="n">
-        <v>11696.43267541223</v>
+        <v>2844.878</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7282,14 +7282,14 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>2009</v>
+        <v>1984</v>
       </c>
       <c r="B328" t="n">
-        <v>0.0974244851347159</v>
+        <v>2993.218</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7305,14 +7305,14 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>2009</v>
+        <v>1985</v>
       </c>
       <c r="B329" t="n">
-        <v>11240.11297133088</v>
+        <v>3158.155</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7328,14 +7328,14 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>2010</v>
+        <v>1986</v>
       </c>
       <c r="B330" t="n">
-        <v>0.0977844044268205</v>
+        <v>3317.184</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7351,14 +7351,14 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2010</v>
+        <v>1987</v>
       </c>
       <c r="B331" t="n">
-        <v>11408.40315225199</v>
+        <v>3459.685</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7374,14 +7374,14 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>2011</v>
+        <v>1988</v>
       </c>
       <c r="B332" t="n">
-        <v>0.0981443237189252</v>
+        <v>3681.151</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>XS006-dcorpnew</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7397,14 +7397,14 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>2011</v>
+        <v>1989</v>
       </c>
       <c r="B333" t="n">
-        <v>11799.35185600587</v>
+        <v>3886.439</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>XS006-depr_only</t>
+          <t>XS006-depr_plus_init</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7486,7 +7486,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GPIM Variant - BEA 1993 Depreciation Rates</t>
+          <t>Generalized Perpetual Inventory Method (GPIM) variant using the BEA 1993 depreciation rates.</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Per Phase 4 Q1: two sub-variants shipped. depr_only matches dossier text; depr_plus_init matches CD2 sample values. Source: Appendix Table 6.8.II.3. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Two sub-variants are shipped: `depr_only` matches the appendix text, and `depr_plus_init` matches the sample values from an earlier replication. Source: Shaikh (2016), Appendix Table 6.8.II.3.</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+          <t>The `-depr_only`, `-depr_plus_init`, and `-dcorpnew` suffixes label the individual sub-variants of this series. The canonical Shaikh-published values are transcribed from the published Chapter 6 appendix workbook (Shaikh 2016, Appendix 6.8). Upstream agencies are the Bureau of Economic Analysis (BEA) — its National Income and Product Accounts (NIPA) and Fixed Asset accounts (FA) — the IRS Statistics of Income (SOI), the U.S. Census Bureau Historical Statistics 1975 (IRS book values), and the Federal Reserve Board G.17 release. All public domain.</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Two sub-variants per Phase 4 Q1:</t>
+          <t>Two sub-variants:</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Book period: 1925-2011. Vintage-stable extension recipe in `XS006_EPR.md`.</t>
+          <t>Book period: 1925-2011. See the companion Extension Provenance Record for the vintage-stable extension recipe.</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>* Two sub-variants shipped per Phase 4 Q1 — see CD2 Divergence in EPR.</t>
+          <t>* Two sub-variants shipped; see the divergence note (versus an earlier replication) in the Extension Provenance Record.</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>`V03_XS006_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>The series round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Two construction dependencies are resolved: the remapping of the NIPA Table 7.11 financial services indirectly measured (FISIM) lines, and the BEA 1993 depreciation rates.</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published XS006 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+          <t>Following the Chapter 6 Generalized Perpetual Inventory Method (GPIM) construction pipeline and the project's anti-degradation rule, **extension does NOT splice the published XS006 values**. Instead, the extension re-fetches the underlying National Income and Product Accounts (NIPA), BEA Fixed Asset, IRS, and Census components and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
@@ -7751,14 +7751,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>1. Fetch the BEA NIPA tables from the BEA API (a BEA API key is required) using the documented primary-source table ids.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 from the same source.</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4. BEA 1993 depreciation/retirement rates are read from `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/BEA_1993_depreciation_retirement_rates.csv` (Phase 5 blocker CH6-B3 RESOLVED). Rate inputs freeze at 2011-vintage projection.</t>
+          <t>4. BEA 1993 depreciation/retirement rates are read from the reconstructed BEA 1993 Fixed Asset methodology inputs. Rate inputs freeze at 2011-vintage projection.</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>For XS006, the Phase 5 round-trip validation reads `XS006_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>For XS006, the round-trip validation reads the raw values from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>## Proxy Use</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
+          <t>No proxies are used in the book period; it is fully sourced from primary BEA / IRS / Census data.</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>## Synthetic Values</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified against the reconstructed BEA 1993 staged inputs).</t>
         </is>
       </c>
     </row>
@@ -7866,35 +7866,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Appendix workbook missing or corrupted | The appendix loader raises a file-not-found error or returns an empty table | Loading fails with an explicit error |</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| Variable name not in workbook | The variable lookup returns no rows | Zero rows are recorded for that subseries and validation flags it as missing |</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| BEA / IRS vintage drift during extension | The re-fetch logs the vintage year; validation tolerance widens for extension rows | Documented per-year; no silent overwrite of the book period |</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| NIPA Table 7.11 financial services indirectly measured (FISIM) line revision (affecting XS003) | The line resolver falls back to the nearest pinned vintage with a logged warning | Re-mapped by label; vintage logged |</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation-rate inputs at 2011-vintage projection | Documented with the reconstructed BEA 1993 Fixed Asset methodology inputs |</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
+          <t>## Divergence From an Earlier Replication</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CD2's S211 sample values match the BEA 1993 *initial* value 77.769 (matches our `XS006-depr_plus_init` sub-variant). The Phase 3 dossier text describes the depreciation-rate-only variant (matches `XS006-depr_only`). Both are shipped; users should inspect Appendix Fig 6.7.5 / 6.7.6 to confirm which Shaikh plots.</t>
+          <t>An earlier replication's sample values match the BEA 1993 *initial* value 77.769 (matching our `XS006-depr_plus_init` sub-variant). The appendix text describes the depreciation-rate-only variant (matching `XS006-depr_only`). Both are shipped; users should inspect Appendix Fig 6.7.5 / 6.7.6 to confirm which Shaikh plots.</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>## Extension Integrity</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>Extension must re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end; splicing the published series is not permitted. Fetched BEA / FRED responses are cached with a 30-day time-to-live (book-period values are cached permanently).</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:49:39.714928+00:00</t>
+          <t>2026-07-02T06:27:23.559621+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS006_extenbook.xlsx
+++ b/extenbooks/XS006_extenbook.xlsx
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:27:23.559621+00:00</t>
+          <t>2026-07-11T03:44:27.534026+00:00</t>
         </is>
       </c>
     </row>
@@ -8308,11 +8308,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8335,6 +8335,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Methodology variant of XS004 isolating the effect of BEA pre-1997 (1993) finite-life depreciation rates, shipped as two sub-variants (depreciation-only on the 2011 initial value; depreciation plus the 1993 initial value). Appendix Table 6.8.II.3. Renders sensibly once units are split: XS006-dcorpnew is the decimal depreciation rate (~0.066-0.098), which must not share the billions axis with the two stock columns (latent mixed-units, fixed here per UNITS_VALIDATION_STANDARD).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS006_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS006_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Per Phase 4 Q1: two sub-variants shipped. depr_only matches dossier text; depr_plus_init matches CD2 sample values. Source: Appendix Table 6.8.II.3. | P2.6 F-P2.1-06: the 1925 initial value 77.769 is the un-rounded BEA Table A.13 figure the construction uses; Shaikh's book prints the rounded 77.7 (the un-rounded value is absent from the KB). Data unchanged (77.769 vs 77.7 = 0.09%, within tol); note clarified so 77.769 is not read as a book-printed number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
